--- a/data/trans_dic/P1418-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1418-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,19</t>
+          <t>3,81; 7,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,61</t>
+          <t>1,97; 4,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,9</t>
+          <t>2,16; 4,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,6</t>
+          <t>3,23; 6,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,66; 11,0</t>
+          <t>6,76; 11,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,7; 12,59</t>
+          <t>7,71; 12,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,88</t>
+          <t>5,61; 10,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,05; 11,06</t>
+          <t>7,86; 11,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,68; 8,4</t>
+          <t>5,68; 8,43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 8,14</t>
+          <t>5,18; 7,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,93</t>
+          <t>4,53; 7,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,12; 8,32</t>
+          <t>5,95; 8,16</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,31</t>
+          <t>4,35; 7,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,97</t>
+          <t>2,58; 5,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,5</t>
+          <t>1,56; 3,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,38</t>
+          <t>3,03; 5,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,77; 11,59</t>
+          <t>7,85; 11,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,37; 12,38</t>
+          <t>8,39; 12,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 7,99</t>
+          <t>4,71; 7,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,29; 9,93</t>
+          <t>7,22; 9,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,54; 8,85</t>
+          <t>6,55; 9,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 8,17</t>
+          <t>5,91; 8,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 5,33</t>
+          <t>3,51; 5,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,51</t>
+          <t>5,39; 7,16</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 7,27</t>
+          <t>3,66; 7,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,99</t>
+          <t>1,81; 5,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,58</t>
+          <t>1,39; 3,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,38</t>
+          <t>3,2; 6,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,13; 13,97</t>
+          <t>9,29; 14,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 9,89</t>
+          <t>5,81; 9,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 9,8</t>
+          <t>5,76; 9,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 8,83</t>
+          <t>6,69; 10,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,8; 9,73</t>
+          <t>6,84; 10,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,31; 6,86</t>
+          <t>4,43; 6,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 6,41</t>
+          <t>3,82; 6,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,84</t>
+          <t>5,31; 7,53</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,04</t>
+          <t>4,27; 7,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,85</t>
+          <t>1,59; 3,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,88</t>
+          <t>1,09; 2,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,25</t>
+          <t>3,15; 5,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,07; 13,11</t>
+          <t>9,23; 13,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,66; 12,49</t>
+          <t>8,75; 12,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,71; 9,41</t>
+          <t>5,78; 9,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 11,16</t>
+          <t>8,01; 10,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,18; 9,65</t>
+          <t>7,24; 9,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,73; 8,0</t>
+          <t>5,67; 7,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 5,74</t>
+          <t>3,72; 5,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 8,27</t>
+          <t>5,96; 7,93</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,71; 6,28</t>
+          <t>4,76; 6,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 3,76</t>
+          <t>2,51; 3,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 2,94</t>
+          <t>1,9; 3,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 4,73</t>
+          <t>3,63; 4,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,14; 11,28</t>
+          <t>9,16; 11,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,72; 10,8</t>
+          <t>8,8; 10,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,3; 8,16</t>
+          <t>6,28; 8,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,89; 9,31</t>
+          <t>8,08; 9,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 8,48</t>
+          <t>7,14; 8,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,92; 7,08</t>
+          <t>5,91; 7,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 5,38</t>
+          <t>4,24; 5,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,34; 6,8</t>
+          <t>6,11; 7,13</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29751</t>
+          <t>31134</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>63753</t>
+          <t>69082</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93503</t>
+          <t>100217</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26560; 49923</t>
+          <t>26456; 50126</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13143; 32408</t>
+          <t>13889; 31675</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15092; 33051</t>
+          <t>14580; 32636</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22225; 41935</t>
+          <t>22285; 44151</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>45854; 75749</t>
+          <t>46530; 75770</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53689; 87753</t>
+          <t>53748; 87555</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38898; 66477</t>
+          <t>37743; 67626</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>54359; 74673</t>
+          <t>57561; 81080</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>78506; 116182</t>
+          <t>78519; 116492</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74530; 114026</t>
+          <t>72521; 111488</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60295; 93446</t>
+          <t>61059; 94755</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>80243; 109060</t>
+          <t>84739; 116137</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36779</t>
+          <t>41198</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>81531</t>
+          <t>89928</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>118309</t>
+          <t>131126</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41060; 70283</t>
+          <t>41866; 70648</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25897; 50626</t>
+          <t>26249; 50871</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16277; 35744</t>
+          <t>15950; 36213</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18905; 52145</t>
+          <t>31750; 55286</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75244; 112277</t>
+          <t>75998; 114940</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>86086; 127342</t>
+          <t>86309; 125305</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50824; 83337</t>
+          <t>49132; 81962</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69654; 94835</t>
+          <t>77075; 104260</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126297; 170850</t>
+          <t>126442; 174636</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>120126; 167173</t>
+          <t>120917; 169663</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73156; 110060</t>
+          <t>72532; 110298</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>77495; 139685</t>
+          <t>113950; 151529</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31290</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58114</t>
+          <t>66226</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89405</t>
+          <t>101788</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25158; 49300</t>
+          <t>24835; 48790</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14640; 37814</t>
+          <t>13728; 38026</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10250; 27216</t>
+          <t>10547; 28012</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23039; 44746</t>
+          <t>25632; 49427</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>62403; 95553</t>
+          <t>63514; 96762</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46600; 76831</t>
+          <t>45115; 76251</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43994; 76940</t>
+          <t>45189; 77408</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30529; 82273</t>
+          <t>54145; 81347</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>92663; 132520</t>
+          <t>93215; 136568</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66153; 105281</t>
+          <t>68031; 104778</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59195; 98952</t>
+          <t>59022; 95961</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>57951; 111680</t>
+          <t>85412; 121129</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41088</t>
+          <t>41670</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>99283</t>
+          <t>103687</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>140370</t>
+          <t>145357</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39836; 66372</t>
+          <t>40190; 66491</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15425; 36466</t>
+          <t>15052; 36088</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10239; 27019</t>
+          <t>10204; 27622</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30924; 57850</t>
+          <t>31145; 57222</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>94191; 136114</t>
+          <t>95818; 136185</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>90955; 131217</t>
+          <t>91998; 128966</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59621; 98270</t>
+          <t>60359; 94648</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>78650; 121644</t>
+          <t>89375; 121199</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>142156; 191085</t>
+          <t>143345; 191087</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>114518; 159817</t>
+          <t>113269; 159354</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>74809; 113638</t>
+          <t>73621; 112623</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>118904; 166703</t>
+          <t>125400; 166890</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>138907</t>
+          <t>149565</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>302680</t>
+          <t>328924</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>441588</t>
+          <t>478489</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>154201; 205646</t>
+          <t>156040; 206738</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>88191; 128787</t>
+          <t>86064; 129575</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64345; 99877</t>
+          <t>64449; 101690</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>109528; 163291</t>
+          <t>127983; 172386</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>308880; 381226</t>
+          <t>309379; 378888</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>309986; 383820</t>
+          <t>312931; 383193</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>223146; 289290</t>
+          <t>222423; 285859</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>251747; 340066</t>
+          <t>301096; 357002</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>482505; 564282</t>
+          <t>475182; 565293</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>413206; 494468</t>
+          <t>412841; 497025</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>301375; 373029</t>
+          <t>294386; 373711</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>379743; 483252</t>
+          <t>443396; 517126</t>
         </is>
       </c>
     </row>
